--- a/ПРАКТИКА инфор.технологии/Практика 5/Задание 3.xlsx
+++ b/ПРАКТИКА инфор.технологии/Практика 5/Задание 3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Second_year_of_college\ПРАКТИКА инфор.технологии\Практика 5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9AEADF-884E-49B0-989D-3267CFC24D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B9C3F8A-52B9-43F6-9014-CA69100913CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Январь" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -470,17 +481,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>15</v>
       </c>
@@ -493,7 +504,7 @@
       <c r="H1" s="12"/>
       <c r="I1" s="12"/>
     </row>
-    <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>7</v>
       </c>
@@ -516,7 +527,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13"/>
       <c r="B3" s="1" t="s">
         <v>2</v>
@@ -537,7 +548,7 @@
       <c r="H3" s="13"/>
       <c r="I3" s="13"/>
     </row>
-    <row r="4" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -569,7 +580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -601,7 +612,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="36.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -633,7 +644,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -665,7 +676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -715,17 +726,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4CEAE87-4CD5-40BE-9470-1CAAF791F5E4}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>15</v>
       </c>
@@ -738,7 +749,7 @@
       <c r="H1" s="12"/>
       <c r="I1" s="12"/>
     </row>
-    <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>7</v>
       </c>
@@ -761,7 +772,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13"/>
       <c r="B3" s="1" t="s">
         <v>2</v>
@@ -782,7 +793,7 @@
       <c r="H3" s="13"/>
       <c r="I3" s="13"/>
     </row>
-    <row r="4" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -814,7 +825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -846,7 +857,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="36.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -878,7 +889,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -910,7 +921,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -959,17 +970,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B53C259D-F755-4375-81BE-36733E08396F}">
   <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>15</v>
       </c>
@@ -982,7 +993,7 @@
       <c r="H1" s="12"/>
       <c r="I1" s="12"/>
     </row>
-    <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>7</v>
       </c>
@@ -1005,7 +1016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="13"/>
       <c r="B3" s="1" t="s">
         <v>2</v>
@@ -1026,7 +1037,7 @@
       <c r="H3" s="13"/>
       <c r="I3" s="13"/>
     </row>
-    <row r="4" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -1058,7 +1069,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -1090,7 +1101,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="36.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -1122,7 +1133,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1154,7 +1165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1203,20 +1214,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68C892AA-9182-4435-B8A4-7CF0C8446B88}">
   <dimension ref="A1:K158"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="7" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="7" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
         <v>16</v>
       </c>
@@ -1229,7 +1240,7 @@
       <c r="J1" s="15"/>
       <c r="K1" s="15"/>
     </row>
-    <row r="2" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1246,7 +1257,7 @@
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" spans="1:11" ht="19.5" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="18" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="5">
         <f>Март!$G$4</f>
@@ -1260,7 +1271,7 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" ht="19.5" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="18" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
       <c r="B4" s="5">
         <f>Февраль!$G$4</f>
@@ -1274,7 +1285,7 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
     </row>
-    <row r="5" spans="1:11" ht="19.5" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="18" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="5">
         <f>Январь!$G$4</f>
@@ -1288,7 +1299,7 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" ht="19.5" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="18" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
@@ -1302,7 +1313,7 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
     </row>
-    <row r="7" spans="1:11" ht="19.5" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="18" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
@@ -1316,7 +1327,7 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" ht="19.5" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="18" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
@@ -1330,7 +1341,7 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
     </row>
-    <row r="9" spans="1:11" ht="19.5" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="18" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
@@ -1344,7 +1355,7 @@
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" ht="19.5" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="18" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
@@ -1358,7 +1369,7 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
     </row>
-    <row r="11" spans="1:11" ht="19.5" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="18" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
@@ -1372,7 +1383,7 @@
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:11" ht="19.5" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="18" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1383,7 +1394,7 @@
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
     </row>
-    <row r="13" spans="1:11" ht="19.5" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="18" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1394,7 +1405,7 @@
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" spans="1:11" ht="19.5" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" ht="18" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -1405,7 +1416,7 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
     </row>
-    <row r="15" spans="1:11" ht="19.5" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="18" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
@@ -1419,7 +1430,7 @@
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" ht="19.5" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="18" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
@@ -1433,7 +1444,7 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
     </row>
-    <row r="17" spans="1:11" ht="19.5" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" ht="18" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
@@ -1447,7 +1458,7 @@
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" ht="18" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
@@ -1461,7 +1472,7 @@
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" ht="18" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
@@ -1475,7 +1486,7 @@
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" ht="18" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
@@ -1489,7 +1500,7 @@
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
     </row>
-    <row r="21" spans="1:11" ht="19.5" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" ht="18" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
@@ -1503,7 +1514,7 @@
       <c r="J21" s="7"/>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" ht="18" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
@@ -1517,7 +1528,7 @@
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
     </row>
-    <row r="23" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" ht="18" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
@@ -1531,7 +1542,7 @@
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" ht="18" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
@@ -1545,7 +1556,7 @@
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
     </row>
-    <row r="25" spans="1:11" ht="19.5" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" ht="18" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
@@ -1559,7 +1570,7 @@
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" ht="18" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
@@ -1573,7 +1584,7 @@
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
     </row>
-    <row r="27" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" ht="18" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
@@ -1587,7 +1598,7 @@
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
     </row>
-    <row r="28" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" ht="18" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
@@ -1601,7 +1612,7 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
     </row>
-    <row r="29" spans="1:11" ht="19.5" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" ht="18" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
@@ -1615,7 +1626,7 @@
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
     </row>
-    <row r="30" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" ht="18" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
@@ -1629,7 +1640,7 @@
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
     </row>
-    <row r="31" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" ht="18" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
@@ -1643,7 +1654,7 @@
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
     </row>
-    <row r="32" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" ht="18" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
@@ -1657,7 +1668,7 @@
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
     </row>
-    <row r="33" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" ht="18" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -1668,7 +1679,7 @@
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
     </row>
-    <row r="34" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" ht="18" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -1679,7 +1690,7 @@
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
     </row>
-    <row r="35" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" ht="18" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -1690,7 +1701,7 @@
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
     </row>
-    <row r="36" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" ht="18" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -1701,7 +1712,7 @@
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
     </row>
-    <row r="37" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" ht="18" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -1712,7 +1723,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
     </row>
-    <row r="38" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" ht="18" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -1723,7 +1734,7 @@
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
     </row>
-    <row r="39" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" ht="18" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -1734,7 +1745,7 @@
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
     </row>
-    <row r="40" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" ht="18" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -1745,7 +1756,7 @@
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
     </row>
-    <row r="41" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" ht="18" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -1756,7 +1767,7 @@
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
     </row>
-    <row r="42" spans="1:11" ht="19.5" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" ht="18.600000000000001" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="2" t="s">
         <v>10</v>
       </c>
@@ -1775,7 +1786,7 @@
       <c r="J42" s="9"/>
       <c r="K42" s="9"/>
     </row>
-    <row r="43" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="2"/>
       <c r="B43" s="6"/>
       <c r="C43" s="11"/>
@@ -1786,7 +1797,7 @@
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
     </row>
-    <row r="44" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="2"/>
       <c r="B44" s="6"/>
       <c r="C44" s="11"/>
@@ -1797,7 +1808,7 @@
       <c r="J44" s="9"/>
       <c r="K44" s="9"/>
     </row>
-    <row r="45" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="2"/>
       <c r="B45" s="6"/>
       <c r="C45" s="11"/>
@@ -1808,7 +1819,7 @@
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
     </row>
-    <row r="46" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="2"/>
       <c r="B46" s="6"/>
       <c r="C46" s="11"/>
@@ -1819,7 +1830,7 @@
       <c r="J46" s="9"/>
       <c r="K46" s="9"/>
     </row>
-    <row r="47" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="2"/>
       <c r="B47" s="6"/>
       <c r="C47" s="11"/>
@@ -1830,7 +1841,7 @@
       <c r="J47" s="9"/>
       <c r="K47" s="9"/>
     </row>
-    <row r="48" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="2"/>
       <c r="B48" s="6"/>
       <c r="C48" s="11"/>
@@ -1841,7 +1852,7 @@
       <c r="J48" s="9"/>
       <c r="K48" s="9"/>
     </row>
-    <row r="49" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="2"/>
       <c r="B49" s="6"/>
       <c r="C49" s="11"/>
@@ -1852,7 +1863,7 @@
       <c r="J49" s="9"/>
       <c r="K49" s="9"/>
     </row>
-    <row r="50" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="2"/>
       <c r="B50" s="6"/>
       <c r="C50" s="11"/>
@@ -1863,7 +1874,7 @@
       <c r="J50" s="9"/>
       <c r="K50" s="9"/>
     </row>
-    <row r="51" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="2"/>
       <c r="B51" s="6"/>
       <c r="C51" s="11"/>
@@ -1874,7 +1885,7 @@
       <c r="J51" s="9"/>
       <c r="K51" s="9"/>
     </row>
-    <row r="52" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="2"/>
       <c r="B52" s="6"/>
       <c r="C52" s="11"/>
@@ -1885,7 +1896,7 @@
       <c r="J52" s="9"/>
       <c r="K52" s="9"/>
     </row>
-    <row r="53" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="2"/>
       <c r="B53" s="6"/>
       <c r="C53" s="11"/>
@@ -1896,7 +1907,7 @@
       <c r="J53" s="9"/>
       <c r="K53" s="9"/>
     </row>
-    <row r="54" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2"/>
       <c r="B54" s="6"/>
       <c r="C54" s="11"/>
@@ -1907,7 +1918,7 @@
       <c r="J54" s="9"/>
       <c r="K54" s="9"/>
     </row>
-    <row r="55" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="2"/>
       <c r="B55" s="6"/>
       <c r="C55" s="11"/>
@@ -1918,7 +1929,7 @@
       <c r="J55" s="9"/>
       <c r="K55" s="9"/>
     </row>
-    <row r="56" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="2"/>
       <c r="B56" s="6"/>
       <c r="C56" s="11"/>
@@ -1929,7 +1940,7 @@
       <c r="J56" s="9"/>
       <c r="K56" s="9"/>
     </row>
-    <row r="57" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="2"/>
       <c r="B57" s="6"/>
       <c r="C57" s="11"/>
@@ -1940,7 +1951,7 @@
       <c r="J57" s="9"/>
       <c r="K57" s="9"/>
     </row>
-    <row r="58" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2"/>
       <c r="B58" s="6"/>
       <c r="C58" s="11"/>
@@ -1951,7 +1962,7 @@
       <c r="J58" s="9"/>
       <c r="K58" s="9"/>
     </row>
-    <row r="59" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2"/>
       <c r="B59" s="6"/>
       <c r="C59" s="11"/>
@@ -1962,7 +1973,7 @@
       <c r="J59" s="9"/>
       <c r="K59" s="9"/>
     </row>
-    <row r="60" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2"/>
       <c r="B60" s="6"/>
       <c r="C60" s="11"/>
@@ -1973,7 +1984,7 @@
       <c r="J60" s="9"/>
       <c r="K60" s="9"/>
     </row>
-    <row r="61" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2"/>
       <c r="B61" s="6"/>
       <c r="C61" s="11"/>
@@ -1984,7 +1995,7 @@
       <c r="J61" s="9"/>
       <c r="K61" s="9"/>
     </row>
-    <row r="62" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="2"/>
       <c r="B62" s="6"/>
       <c r="C62" s="11"/>
@@ -1995,7 +2006,7 @@
       <c r="J62" s="9"/>
       <c r="K62" s="9"/>
     </row>
-    <row r="63" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="2"/>
       <c r="B63" s="6"/>
       <c r="C63" s="11"/>
@@ -2006,7 +2017,7 @@
       <c r="J63" s="9"/>
       <c r="K63" s="9"/>
     </row>
-    <row r="64" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="2"/>
       <c r="B64" s="6"/>
       <c r="C64" s="11"/>
@@ -2017,7 +2028,7 @@
       <c r="J64" s="9"/>
       <c r="K64" s="9"/>
     </row>
-    <row r="65" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="2"/>
       <c r="B65" s="6"/>
       <c r="C65" s="11"/>
@@ -2028,7 +2039,7 @@
       <c r="J65" s="9"/>
       <c r="K65" s="9"/>
     </row>
-    <row r="66" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="2"/>
       <c r="B66" s="6"/>
       <c r="C66" s="11"/>
@@ -2039,7 +2050,7 @@
       <c r="J66" s="9"/>
       <c r="K66" s="9"/>
     </row>
-    <row r="67" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="2"/>
       <c r="B67" s="6"/>
       <c r="C67" s="11"/>
@@ -2050,7 +2061,7 @@
       <c r="J67" s="9"/>
       <c r="K67" s="9"/>
     </row>
-    <row r="68" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="2"/>
       <c r="B68" s="6"/>
       <c r="C68" s="11"/>
@@ -2061,7 +2072,7 @@
       <c r="J68" s="9"/>
       <c r="K68" s="9"/>
     </row>
-    <row r="69" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="2"/>
       <c r="B69" s="6"/>
       <c r="C69" s="11"/>
@@ -2072,7 +2083,7 @@
       <c r="J69" s="9"/>
       <c r="K69" s="9"/>
     </row>
-    <row r="70" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="2"/>
       <c r="B70" s="6"/>
       <c r="C70" s="11">
@@ -2086,7 +2097,7 @@
       <c r="J70" s="9"/>
       <c r="K70" s="9"/>
     </row>
-    <row r="71" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="2"/>
       <c r="B71" s="6"/>
       <c r="C71" s="11"/>
@@ -2097,7 +2108,7 @@
       <c r="J71" s="9"/>
       <c r="K71" s="9"/>
     </row>
-    <row r="72" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="2"/>
       <c r="B72" s="6"/>
       <c r="C72" s="11"/>
@@ -2108,7 +2119,7 @@
       <c r="J72" s="9"/>
       <c r="K72" s="9"/>
     </row>
-    <row r="73" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="2"/>
       <c r="B73" s="6"/>
       <c r="C73" s="11"/>
@@ -2119,7 +2130,7 @@
       <c r="J73" s="9"/>
       <c r="K73" s="9"/>
     </row>
-    <row r="74" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="2"/>
       <c r="B74" s="6"/>
       <c r="C74" s="11">
@@ -2133,7 +2144,7 @@
       <c r="J74" s="9"/>
       <c r="K74" s="9"/>
     </row>
-    <row r="75" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="2"/>
       <c r="B75" s="6"/>
       <c r="C75" s="11"/>
@@ -2144,7 +2155,7 @@
       <c r="J75" s="9"/>
       <c r="K75" s="9"/>
     </row>
-    <row r="76" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="2"/>
       <c r="B76" s="6"/>
       <c r="C76" s="11"/>
@@ -2155,7 +2166,7 @@
       <c r="J76" s="9"/>
       <c r="K76" s="9"/>
     </row>
-    <row r="77" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="2"/>
       <c r="B77" s="6"/>
       <c r="C77" s="11"/>
@@ -2166,7 +2177,7 @@
       <c r="J77" s="9"/>
       <c r="K77" s="9"/>
     </row>
-    <row r="78" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="2"/>
       <c r="B78" s="6"/>
       <c r="C78" s="11">
@@ -2180,7 +2191,7 @@
       <c r="J78" s="9"/>
       <c r="K78" s="9"/>
     </row>
-    <row r="79" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="2"/>
       <c r="B79" s="6"/>
       <c r="C79" s="11"/>
@@ -2191,7 +2202,7 @@
       <c r="J79" s="9"/>
       <c r="K79" s="9"/>
     </row>
-    <row r="80" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="2"/>
       <c r="B80" s="6"/>
       <c r="C80" s="11"/>
@@ -2202,7 +2213,7 @@
       <c r="J80" s="9"/>
       <c r="K80" s="9"/>
     </row>
-    <row r="81" spans="1:11" ht="19.5" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="7" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="2"/>
       <c r="B81" s="6"/>
       <c r="C81" s="11"/>
@@ -2213,7 +2224,7 @@
       <c r="J81" s="9"/>
       <c r="K81" s="9"/>
     </row>
-    <row r="82" spans="1:11" ht="19.5" hidden="1" outlineLevel="6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="2"/>
       <c r="B82" s="6"/>
       <c r="C82" s="11">
@@ -2227,7 +2238,7 @@
       <c r="J82" s="9"/>
       <c r="K82" s="9"/>
     </row>
-    <row r="83" spans="1:11" ht="19.5" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="2"/>
       <c r="B83" s="6"/>
       <c r="C83" s="11">
@@ -2241,7 +2252,7 @@
       <c r="J83" s="9"/>
       <c r="K83" s="9"/>
     </row>
-    <row r="84" spans="1:11" ht="19.5" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="2"/>
       <c r="B84" s="6"/>
       <c r="C84" s="11">
@@ -2255,7 +2266,7 @@
       <c r="J84" s="9"/>
       <c r="K84" s="9"/>
     </row>
-    <row r="85" spans="1:11" ht="19.5" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="2"/>
       <c r="B85" s="6"/>
       <c r="C85" s="11">
@@ -2269,7 +2280,7 @@
       <c r="J85" s="9"/>
       <c r="K85" s="9"/>
     </row>
-    <row r="86" spans="1:11" ht="19.5" hidden="1" outlineLevel="6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="2"/>
       <c r="B86" s="6"/>
       <c r="C86" s="11">
@@ -2283,7 +2294,7 @@
       <c r="J86" s="9"/>
       <c r="K86" s="9"/>
     </row>
-    <row r="87" spans="1:11" ht="19.5" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="2"/>
       <c r="B87" s="6"/>
       <c r="C87" s="11">
@@ -2297,7 +2308,7 @@
       <c r="J87" s="9"/>
       <c r="K87" s="9"/>
     </row>
-    <row r="88" spans="1:11" ht="19.5" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="2"/>
       <c r="B88" s="6"/>
       <c r="C88" s="11">
@@ -2311,7 +2322,7 @@
       <c r="J88" s="9"/>
       <c r="K88" s="9"/>
     </row>
-    <row r="89" spans="1:11" ht="19.5" hidden="1" outlineLevel="5" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="5" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="2"/>
       <c r="B89" s="6"/>
       <c r="C89" s="11">
@@ -2325,7 +2336,7 @@
       <c r="J89" s="9"/>
       <c r="K89" s="9"/>
     </row>
-    <row r="90" spans="1:11" ht="19.5" hidden="1" outlineLevel="6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="2"/>
       <c r="B90" s="6"/>
       <c r="C90" s="11">
@@ -2339,7 +2350,7 @@
       <c r="J90" s="9"/>
       <c r="K90" s="9"/>
     </row>
-    <row r="91" spans="1:11" ht="19.5" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="2"/>
       <c r="B91" s="6"/>
       <c r="C91" s="11">
@@ -2353,7 +2364,7 @@
       <c r="J91" s="9"/>
       <c r="K91" s="9"/>
     </row>
-    <row r="92" spans="1:11" ht="19.5" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="6" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="2"/>
       <c r="B92" s="6"/>
       <c r="C92" s="11">
@@ -2367,7 +2378,7 @@
       <c r="J92" s="9"/>
       <c r="K92" s="9"/>
     </row>
-    <row r="93" spans="1:11" ht="19.5" hidden="1" outlineLevel="5" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="5" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="2"/>
       <c r="B93" s="6"/>
       <c r="C93" s="11">
@@ -2381,7 +2392,7 @@
       <c r="J93" s="9"/>
       <c r="K93" s="9"/>
     </row>
-    <row r="94" spans="1:11" ht="19.5" hidden="1" outlineLevel="6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="2"/>
       <c r="B94" s="6"/>
       <c r="C94" s="11">
@@ -2395,7 +2406,7 @@
       <c r="J94" s="9"/>
       <c r="K94" s="9"/>
     </row>
-    <row r="95" spans="1:11" ht="19.5" hidden="1" outlineLevel="6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="2"/>
       <c r="B95" s="6"/>
       <c r="C95" s="11">
@@ -2409,7 +2420,7 @@
       <c r="J95" s="9"/>
       <c r="K95" s="9"/>
     </row>
-    <row r="96" spans="1:11" ht="19.5" hidden="1" outlineLevel="6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="2"/>
       <c r="B96" s="6"/>
       <c r="C96" s="11">
@@ -2423,7 +2434,7 @@
       <c r="J96" s="9"/>
       <c r="K96" s="9"/>
     </row>
-    <row r="97" spans="1:11" ht="19.5" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="2"/>
       <c r="B97" s="6"/>
       <c r="C97" s="11">
@@ -2437,7 +2448,7 @@
       <c r="J97" s="9"/>
       <c r="K97" s="9"/>
     </row>
-    <row r="98" spans="1:11" ht="19.5" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="2"/>
       <c r="B98" s="6"/>
       <c r="C98" s="11">
@@ -2451,7 +2462,7 @@
       <c r="J98" s="9"/>
       <c r="K98" s="9"/>
     </row>
-    <row r="99" spans="1:11" ht="19.5" hidden="1" outlineLevel="5" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="5" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="2"/>
       <c r="B99" s="6"/>
       <c r="C99" s="11">
@@ -2465,7 +2476,7 @@
       <c r="J99" s="9"/>
       <c r="K99" s="9"/>
     </row>
-    <row r="100" spans="1:11" ht="19.5" hidden="1" outlineLevel="5" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="5" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="2"/>
       <c r="B100" s="6"/>
       <c r="C100" s="11">
@@ -2479,7 +2490,7 @@
       <c r="J100" s="9"/>
       <c r="K100" s="9"/>
     </row>
-    <row r="101" spans="1:11" ht="19.5" hidden="1" outlineLevel="4" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="4" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="2"/>
       <c r="B101" s="6"/>
       <c r="C101" s="11">
@@ -2493,7 +2504,7 @@
       <c r="J101" s="9"/>
       <c r="K101" s="9"/>
     </row>
-    <row r="102" spans="1:11" ht="19.5" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="2"/>
       <c r="B102" s="6"/>
       <c r="C102" s="11">
@@ -2507,7 +2518,7 @@
       <c r="J102" s="9"/>
       <c r="K102" s="9"/>
     </row>
-    <row r="103" spans="1:11" ht="19.5" hidden="1" outlineLevel="5" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="5" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="2"/>
       <c r="B103" s="6"/>
       <c r="C103" s="11">
@@ -2521,7 +2532,7 @@
       <c r="J103" s="9"/>
       <c r="K103" s="9"/>
     </row>
-    <row r="104" spans="1:11" ht="19.5" hidden="1" outlineLevel="5" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="5" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="2"/>
       <c r="B104" s="6"/>
       <c r="C104" s="11">
@@ -2535,7 +2546,7 @@
       <c r="J104" s="9"/>
       <c r="K104" s="9"/>
     </row>
-    <row r="105" spans="1:11" ht="19.5" hidden="1" outlineLevel="4" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="4" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="2"/>
       <c r="B105" s="6"/>
       <c r="C105" s="11">
@@ -2549,7 +2560,7 @@
       <c r="J105" s="9"/>
       <c r="K105" s="9"/>
     </row>
-    <row r="106" spans="1:11" ht="19.5" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="2"/>
       <c r="B106" s="6"/>
       <c r="C106" s="11">
@@ -2563,7 +2574,7 @@
       <c r="J106" s="9"/>
       <c r="K106" s="9"/>
     </row>
-    <row r="107" spans="1:11" ht="19.5" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="2"/>
       <c r="B107" s="6"/>
       <c r="C107" s="11">
@@ -2577,7 +2588,7 @@
       <c r="J107" s="9"/>
       <c r="K107" s="9"/>
     </row>
-    <row r="108" spans="1:11" ht="19.5" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="2"/>
       <c r="B108" s="6"/>
       <c r="C108" s="11">
@@ -2591,7 +2602,7 @@
       <c r="J108" s="9"/>
       <c r="K108" s="9"/>
     </row>
-    <row r="109" spans="1:11" ht="19.5" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="2"/>
       <c r="B109" s="6"/>
       <c r="C109" s="11">
@@ -2605,7 +2616,7 @@
       <c r="J109" s="9"/>
       <c r="K109" s="9"/>
     </row>
-    <row r="110" spans="1:11" ht="19.5" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="2"/>
       <c r="B110" s="6"/>
       <c r="C110" s="11">
@@ -2619,7 +2630,7 @@
       <c r="J110" s="9"/>
       <c r="K110" s="9"/>
     </row>
-    <row r="111" spans="1:11" ht="19.5" hidden="1" outlineLevel="4" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="4" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="2"/>
       <c r="B111" s="6"/>
       <c r="C111" s="11">
@@ -2633,7 +2644,7 @@
       <c r="J111" s="9"/>
       <c r="K111" s="9"/>
     </row>
-    <row r="112" spans="1:11" ht="19.5" hidden="1" outlineLevel="4" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="4" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="2"/>
       <c r="B112" s="6"/>
       <c r="C112" s="11">
@@ -2647,7 +2658,7 @@
       <c r="J112" s="9"/>
       <c r="K112" s="9"/>
     </row>
-    <row r="113" spans="1:11" ht="19.5" hidden="1" outlineLevel="3" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="3" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="2"/>
       <c r="B113" s="6"/>
       <c r="C113" s="11">
@@ -2661,7 +2672,7 @@
       <c r="J113" s="9"/>
       <c r="K113" s="9"/>
     </row>
-    <row r="114" spans="1:11" ht="19.5" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="2"/>
       <c r="B114" s="6"/>
       <c r="C114" s="11">
@@ -2675,7 +2686,7 @@
       <c r="J114" s="9"/>
       <c r="K114" s="9"/>
     </row>
-    <row r="115" spans="1:11" ht="19.5" hidden="1" outlineLevel="4" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="4" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="2"/>
       <c r="B115" s="6"/>
       <c r="C115" s="11">
@@ -2689,7 +2700,7 @@
       <c r="J115" s="9"/>
       <c r="K115" s="9"/>
     </row>
-    <row r="116" spans="1:11" ht="19.5" hidden="1" outlineLevel="4" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="4" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="2"/>
       <c r="B116" s="6"/>
       <c r="C116" s="11">
@@ -2703,7 +2714,7 @@
       <c r="J116" s="9"/>
       <c r="K116" s="9"/>
     </row>
-    <row r="117" spans="1:11" ht="19.5" hidden="1" outlineLevel="3" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="3" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="2"/>
       <c r="B117" s="6"/>
       <c r="C117" s="11">
@@ -2717,7 +2728,7 @@
       <c r="J117" s="9"/>
       <c r="K117" s="9"/>
     </row>
-    <row r="118" spans="1:11" ht="19.5" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="2"/>
       <c r="B118" s="6"/>
       <c r="C118" s="11">
@@ -2731,7 +2742,7 @@
       <c r="J118" s="9"/>
       <c r="K118" s="9"/>
     </row>
-    <row r="119" spans="1:11" ht="19.5" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="2"/>
       <c r="B119" s="6"/>
       <c r="C119" s="11">
@@ -2745,7 +2756,7 @@
       <c r="J119" s="9"/>
       <c r="K119" s="9"/>
     </row>
-    <row r="120" spans="1:11" ht="19.5" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="4" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="2"/>
       <c r="B120" s="6"/>
       <c r="C120" s="11">
@@ -2759,7 +2770,7 @@
       <c r="J120" s="9"/>
       <c r="K120" s="9"/>
     </row>
-    <row r="121" spans="1:11" ht="19.5" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="2"/>
       <c r="B121" s="6"/>
       <c r="C121" s="11">
@@ -2773,7 +2784,7 @@
       <c r="J121" s="9"/>
       <c r="K121" s="9"/>
     </row>
-    <row r="122" spans="1:11" ht="19.5" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="2"/>
       <c r="B122" s="6"/>
       <c r="C122" s="11">
@@ -2787,7 +2798,7 @@
       <c r="J122" s="9"/>
       <c r="K122" s="9"/>
     </row>
-    <row r="123" spans="1:11" ht="19.5" hidden="1" outlineLevel="3" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="3" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="2"/>
       <c r="B123" s="6"/>
       <c r="C123" s="11">
@@ -2801,7 +2812,7 @@
       <c r="J123" s="9"/>
       <c r="K123" s="9"/>
     </row>
-    <row r="124" spans="1:11" ht="19.5" hidden="1" outlineLevel="3" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="3" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="2"/>
       <c r="B124" s="6"/>
       <c r="C124" s="11">
@@ -2815,7 +2826,7 @@
       <c r="J124" s="9"/>
       <c r="K124" s="9"/>
     </row>
-    <row r="125" spans="1:11" ht="19.5" hidden="1" outlineLevel="2" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="2" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="2"/>
       <c r="B125" s="6"/>
       <c r="C125" s="11">
@@ -2829,7 +2840,7 @@
       <c r="J125" s="9"/>
       <c r="K125" s="9"/>
     </row>
-    <row r="126" spans="1:11" ht="19.5" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="2"/>
       <c r="B126" s="6"/>
       <c r="C126" s="11">
@@ -2843,7 +2854,7 @@
       <c r="J126" s="9"/>
       <c r="K126" s="9"/>
     </row>
-    <row r="127" spans="1:11" ht="19.5" hidden="1" outlineLevel="3" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="3" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="2"/>
       <c r="B127" s="6"/>
       <c r="C127" s="11">
@@ -2857,7 +2868,7 @@
       <c r="J127" s="9"/>
       <c r="K127" s="9"/>
     </row>
-    <row r="128" spans="1:11" ht="19.5" hidden="1" outlineLevel="3" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="3" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="2"/>
       <c r="B128" s="6"/>
       <c r="C128" s="11">
@@ -2871,7 +2882,7 @@
       <c r="J128" s="9"/>
       <c r="K128" s="9"/>
     </row>
-    <row r="129" spans="1:11" ht="19.5" hidden="1" outlineLevel="2" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="2" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="2"/>
       <c r="B129" s="6"/>
       <c r="C129" s="11">
@@ -2885,7 +2896,7 @@
       <c r="J129" s="9"/>
       <c r="K129" s="9"/>
     </row>
-    <row r="130" spans="1:11" ht="19.5" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="2"/>
       <c r="B130" s="6"/>
       <c r="C130" s="11">
@@ -2899,7 +2910,7 @@
       <c r="J130" s="9"/>
       <c r="K130" s="9"/>
     </row>
-    <row r="131" spans="1:11" ht="19.5" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="2"/>
       <c r="B131" s="6"/>
       <c r="C131" s="11">
@@ -2913,7 +2924,7 @@
       <c r="J131" s="9"/>
       <c r="K131" s="9"/>
     </row>
-    <row r="132" spans="1:11" ht="19.5" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="3" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="2"/>
       <c r="B132" s="6"/>
       <c r="C132" s="11">
@@ -2927,7 +2938,7 @@
       <c r="J132" s="9"/>
       <c r="K132" s="9"/>
     </row>
-    <row r="133" spans="1:11" ht="19.5" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="2"/>
       <c r="B133" s="6">
         <f>Март!$G$5</f>
@@ -2944,7 +2955,7 @@
       <c r="J133" s="9"/>
       <c r="K133" s="9"/>
     </row>
-    <row r="134" spans="1:11" ht="19.5" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="2"/>
       <c r="B134" s="6"/>
       <c r="C134" s="11">
@@ -2958,7 +2969,7 @@
       <c r="J134" s="9"/>
       <c r="K134" s="9"/>
     </row>
-    <row r="135" spans="1:11" ht="19.5" hidden="1" outlineLevel="2" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="2" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="2"/>
       <c r="B135" s="6"/>
       <c r="C135" s="11">
@@ -2972,7 +2983,7 @@
       <c r="J135" s="9"/>
       <c r="K135" s="9"/>
     </row>
-    <row r="136" spans="1:11" ht="19.5" hidden="1" outlineLevel="2" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="2" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="2"/>
       <c r="B136" s="6"/>
       <c r="C136" s="11">
@@ -2986,7 +2997,7 @@
       <c r="J136" s="9"/>
       <c r="K136" s="9"/>
     </row>
-    <row r="137" spans="1:11" ht="19.5" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="2"/>
       <c r="B137" s="6">
         <f>Февраль!$G$5</f>
@@ -3003,7 +3014,7 @@
       <c r="J137" s="9"/>
       <c r="K137" s="9"/>
     </row>
-    <row r="138" spans="1:11" ht="19.5" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="2"/>
       <c r="B138" s="6"/>
       <c r="C138" s="11">
@@ -3017,7 +3028,7 @@
       <c r="J138" s="9"/>
       <c r="K138" s="9"/>
     </row>
-    <row r="139" spans="1:11" ht="19.5" hidden="1" outlineLevel="2" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="2" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="2"/>
       <c r="B139" s="6"/>
       <c r="C139" s="11">
@@ -3031,7 +3042,7 @@
       <c r="J139" s="9"/>
       <c r="K139" s="9"/>
     </row>
-    <row r="140" spans="1:11" ht="19.5" hidden="1" outlineLevel="2" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="2" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="2"/>
       <c r="B140" s="6"/>
       <c r="C140" s="11">
@@ -3045,7 +3056,7 @@
       <c r="J140" s="9"/>
       <c r="K140" s="9"/>
     </row>
-    <row r="141" spans="1:11" ht="19.5" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="2"/>
       <c r="B141" s="6">
         <f>Январь!$G$5</f>
@@ -3062,7 +3073,7 @@
       <c r="J141" s="9"/>
       <c r="K141" s="9"/>
     </row>
-    <row r="142" spans="1:11" ht="19.5" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="2"/>
       <c r="B142" s="6"/>
       <c r="C142" s="11">
@@ -3076,7 +3087,7 @@
       <c r="J142" s="9"/>
       <c r="K142" s="9"/>
     </row>
-    <row r="143" spans="1:11" ht="19.5" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="2"/>
       <c r="B143" s="6"/>
       <c r="C143" s="11">
@@ -3090,7 +3101,7 @@
       <c r="J143" s="9"/>
       <c r="K143" s="9"/>
     </row>
-    <row r="144" spans="1:11" ht="19.5" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="2" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="2"/>
       <c r="B144" s="6"/>
       <c r="C144" s="11">
@@ -3104,7 +3115,7 @@
       <c r="J144" s="9"/>
       <c r="K144" s="9"/>
     </row>
-    <row r="145" spans="1:11" ht="19.5" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" ht="18.600000000000001" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="2" t="s">
         <v>11</v>
       </c>
@@ -3112,7 +3123,7 @@
         <f>SUM(B133:B141)</f>
         <v>36</v>
       </c>
-      <c r="C145" s="6">
+      <c r="C145" s="11">
         <f t="shared" si="1"/>
         <v>5.7207848732377785E+21</v>
       </c>
@@ -3123,7 +3134,7 @@
       <c r="J145" s="9"/>
       <c r="K145" s="9"/>
     </row>
-    <row r="146" spans="1:11" ht="19.5" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="2"/>
       <c r="B146" s="6">
         <f>Март!$G$6</f>
@@ -3140,7 +3151,7 @@
       <c r="J146" s="9"/>
       <c r="K146" s="9"/>
     </row>
-    <row r="147" spans="1:11" ht="19.5" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="2"/>
       <c r="B147" s="6">
         <f>Февраль!$G$6</f>
@@ -3157,7 +3168,7 @@
       <c r="J147" s="9"/>
       <c r="K147" s="9"/>
     </row>
-    <row r="148" spans="1:11" ht="19.5" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="2"/>
       <c r="B148" s="6">
         <f>Январь!$G$6</f>
@@ -3174,7 +3185,7 @@
       <c r="J148" s="9"/>
       <c r="K148" s="9"/>
     </row>
-    <row r="149" spans="1:11" ht="38.25" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" ht="36.6" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="4" t="s">
         <v>12</v>
       </c>
@@ -3182,7 +3193,7 @@
         <f>SUM(B146:B148)</f>
         <v>48</v>
       </c>
-      <c r="C149" s="6">
+      <c r="C149" s="11">
         <f t="shared" si="1"/>
         <v>6.5471665765925238E+22</v>
       </c>
@@ -3193,13 +3204,13 @@
       <c r="J149" s="9"/>
       <c r="K149" s="9"/>
     </row>
-    <row r="150" spans="1:11" ht="19.5" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="4"/>
       <c r="B150" s="6">
         <f>Март!$G$7</f>
         <v>10</v>
       </c>
-      <c r="C150" s="6">
+      <c r="C150" s="11">
         <f t="shared" si="1"/>
         <v>1.204211676850747E+23</v>
       </c>
@@ -3210,13 +3221,13 @@
       <c r="J150" s="9"/>
       <c r="K150" s="9"/>
     </row>
-    <row r="151" spans="1:11" ht="19.5" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="4"/>
       <c r="B151" s="6">
         <f>Февраль!$G$7</f>
         <v>10</v>
       </c>
-      <c r="C151" s="6">
+      <c r="C151" s="11">
         <f t="shared" si="1"/>
         <v>2.2148905877058144E+23</v>
       </c>
@@ -3227,13 +3238,13 @@
       <c r="J151" s="9"/>
       <c r="K151" s="9"/>
     </row>
-    <row r="152" spans="1:11" ht="19.5" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="4"/>
       <c r="B152" s="6">
         <f>Январь!$G$7</f>
         <v>10</v>
       </c>
-      <c r="C152" s="6">
+      <c r="C152" s="11">
         <f t="shared" si="1"/>
         <v>4.0738189222158139E+23</v>
       </c>
@@ -3244,7 +3255,7 @@
       <c r="J152" s="9"/>
       <c r="K152" s="9"/>
     </row>
-    <row r="153" spans="1:11" ht="19.5" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" ht="18.600000000000001" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="2" t="s">
         <v>13</v>
       </c>
@@ -3252,7 +3263,7 @@
         <f>SUM(B150:B152)</f>
         <v>30</v>
       </c>
-      <c r="C153" s="6">
+      <c r="C153" s="11">
         <f t="shared" si="1"/>
         <v>7.4929211867723749E+23</v>
       </c>
@@ -3263,13 +3274,13 @@
       <c r="J153" s="9"/>
       <c r="K153" s="9"/>
     </row>
-    <row r="154" spans="1:11" ht="19.5" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="2"/>
       <c r="B154" s="6">
         <f>Март!$G$8</f>
         <v>91</v>
       </c>
-      <c r="C154" s="6">
+      <c r="C154" s="11">
         <f t="shared" si="1"/>
         <v>1.3781630696694003E+24</v>
       </c>
@@ -3280,13 +3291,13 @@
       <c r="J154" s="9"/>
       <c r="K154" s="9"/>
     </row>
-    <row r="155" spans="1:11" ht="19.5" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="2"/>
       <c r="B155" s="6">
         <f>Февраль!$G$8</f>
         <v>91</v>
       </c>
-      <c r="C155" s="6">
+      <c r="C155" s="11">
         <f t="shared" si="1"/>
         <v>2.5348370805682191E+24</v>
       </c>
@@ -3297,13 +3308,13 @@
       <c r="J155" s="9"/>
       <c r="K155" s="9"/>
     </row>
-    <row r="156" spans="1:11" ht="19.5" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" ht="18.600000000000001" hidden="1" outlineLevel="1" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="2"/>
       <c r="B156" s="6">
         <f>Январь!$G$8</f>
         <v>91</v>
       </c>
-      <c r="C156" s="6">
+      <c r="C156" s="11">
         <f t="shared" si="1"/>
         <v>4.662292268914857E+24</v>
       </c>
@@ -3314,7 +3325,7 @@
       <c r="J156" s="9"/>
       <c r="K156" s="9"/>
     </row>
-    <row r="157" spans="1:11" ht="19.5" collapsed="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" ht="18.600000000000001" collapsed="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="2" t="s">
         <v>14</v>
       </c>
@@ -3322,7 +3333,7 @@
         <f>SUM(B154:B156)</f>
         <v>273</v>
       </c>
-      <c r="C157" s="6">
+      <c r="C157" s="11">
         <f t="shared" si="1"/>
         <v>8.575292419152477E+24</v>
       </c>
@@ -3332,7 +3343,7 @@
       <c r="J157" s="9"/>
       <c r="K157" s="9"/>
     </row>
-    <row r="158" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" ht="18" x14ac:dyDescent="0.3">
       <c r="C158" s="9"/>
     </row>
   </sheetData>
